--- a/dataset/91_USER_UPLOAD_UNPUB.xlsx
+++ b/dataset/91_USER_UPLOAD_UNPUB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" checkCompatibility="1" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toyoho/Documents/study/704-Python/Webアプリ_main134_20230513/Streamlit/streamlit_main_ongoing20260316_Atwood_大整理/dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/toyoho/Documents/GitHub/test2/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032AA3F8-FA43-0C48-B88C-32D73EBC216D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AF6313-4620-9446-B299-BC0599593C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5080" yWindow="2800" windowWidth="38400" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Station</t>
     <phoneticPr fontId="3"/>
@@ -153,21 +153,6 @@
   </si>
   <si>
     <t>reference</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Kitajima</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Kodama et al. (2024)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>14_5</t>
-  </si>
-  <si>
-    <t>sample data</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -789,20 +774,6 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>参考データを５行入力してあります（←消して頂いて大丈夫です）</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
             <a:t>○１行目の赤文字の黄色セルは入力推奨です（データが無ければ空欄で</a:t>
           </a:r>
           <a:r>
@@ -1059,13 +1030,6 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:br>
-            <a:rPr lang="ja-JP" altLang="en-US"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en" altLang="ja-JP" b="1"/>
-            <a:t>Five rows of sample data are provided (you may delete them if unnecessary).</a:t>
-          </a:r>
           <a:endParaRPr lang="en" altLang="ja-JP"/>
         </a:p>
         <a:p>
@@ -1099,11 +1063,64 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>20818</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>72869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>919785</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>10410</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CFA9F2C-B34D-B69D-0852-F28DBD602953}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="988933" y="4674017"/>
+          <a:ext cx="17117491" cy="999344"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="127000" cap="sq">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="57150" dist="50800" dir="2700000" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="40000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1534,347 +1551,124 @@
       </c>
     </row>
     <row r="2" spans="1:24" s="10" customFormat="1">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="12">
-        <v>13</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="13">
-        <v>42439</v>
-      </c>
-      <c r="E2" s="14">
-        <f t="shared" ref="E2:E6" si="0">YEAR(D2)</f>
-        <v>2016</v>
-      </c>
-      <c r="F2" s="14">
-        <f t="shared" ref="F2:F6" si="1">MONTH(D2)</f>
-        <v>3</v>
-      </c>
-      <c r="G2" s="15">
-        <f t="shared" ref="G2:G6" si="2">DAY(D2)</f>
-        <v>10</v>
-      </c>
-      <c r="H2" s="16">
-        <v>0.90277777777777779</v>
-      </c>
-      <c r="I2" s="17">
-        <v>126.76926666666667</v>
-      </c>
-      <c r="J2" s="17">
-        <v>31.750699999999998</v>
-      </c>
-      <c r="K2" s="18">
-        <v>0</v>
-      </c>
-      <c r="L2" s="18">
-        <v>0</v>
-      </c>
-      <c r="M2" s="18">
-        <v>0</v>
-      </c>
-      <c r="N2" s="19">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="O2" s="20">
-        <v>34.659362283430269</v>
-      </c>
-      <c r="P2" s="21">
-        <v>0.27700000000000002</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>1.869</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
       <c r="R2" s="21"/>
-      <c r="S2" s="12" t="s">
-        <v>24</v>
-      </c>
+      <c r="S2" s="12"/>
       <c r="T2" s="12"/>
-      <c r="U2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="U2" s="12"/>
+      <c r="V2" s="4"/>
     </row>
     <row r="3" spans="1:24" s="10" customFormat="1">
-      <c r="A3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="13">
-        <v>42440</v>
-      </c>
-      <c r="E3" s="14">
-        <f t="shared" si="0"/>
-        <v>2016</v>
-      </c>
-      <c r="F3" s="14">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="G3" s="15">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="H3" s="16">
-        <v>4.6527777777777779E-2</v>
-      </c>
-      <c r="I3" s="17">
-        <v>127.23175000000001</v>
-      </c>
-      <c r="J3" s="17">
-        <v>31.747033333333334</v>
-      </c>
-      <c r="K3" s="18">
-        <v>0</v>
-      </c>
-      <c r="L3" s="18">
-        <v>0</v>
-      </c>
-      <c r="M3" s="18">
-        <v>0</v>
-      </c>
-      <c r="N3" s="19">
-        <v>15.5</v>
-      </c>
-      <c r="O3" s="20">
-        <v>34.576365674671749</v>
-      </c>
-      <c r="P3" s="21">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="Q3" s="21">
-        <v>1.34</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
-      <c r="S3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="12">
-        <v>1</v>
-      </c>
-      <c r="U3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="4"/>
     </row>
     <row r="4" spans="1:24" s="10" customFormat="1">
-      <c r="A4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="13">
-        <v>42440</v>
-      </c>
-      <c r="E4" s="14">
-        <f t="shared" si="0"/>
-        <v>2016</v>
-      </c>
-      <c r="F4" s="14">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="G4" s="15">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="H4" s="16">
-        <v>4.6527777777777779E-2</v>
-      </c>
-      <c r="I4" s="17">
-        <v>127.23175000000001</v>
-      </c>
-      <c r="J4" s="17">
-        <v>31.747033333333334</v>
-      </c>
-      <c r="K4" s="18">
-        <v>10.215</v>
-      </c>
-      <c r="L4" s="18">
-        <v>10</v>
-      </c>
-      <c r="M4" s="18">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19">
-        <v>15.934799999999999</v>
-      </c>
-      <c r="O4" s="20">
-        <v>34.5505</v>
-      </c>
-      <c r="P4" s="21">
-        <v>0.19400000000000001</v>
-      </c>
-      <c r="Q4" s="21">
-        <v>1.357</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
       <c r="R4" s="21"/>
-      <c r="S4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="12">
-        <v>1</v>
-      </c>
-      <c r="U4" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="4"/>
     </row>
     <row r="5" spans="1:24" s="10" customFormat="1">
-      <c r="A5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="13">
-        <v>42440</v>
-      </c>
-      <c r="E5" s="14">
-        <f t="shared" si="0"/>
-        <v>2016</v>
-      </c>
-      <c r="F5" s="14">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="G5" s="15">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="H5" s="16">
-        <v>4.6527777777777779E-2</v>
-      </c>
-      <c r="I5" s="17">
-        <v>127.23175000000001</v>
-      </c>
-      <c r="J5" s="17">
-        <v>31.747033333333334</v>
-      </c>
-      <c r="K5" s="18">
-        <v>21.05</v>
-      </c>
-      <c r="L5" s="18">
-        <v>20</v>
-      </c>
-      <c r="M5" s="18">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19">
-        <v>15.932600000000001</v>
-      </c>
-      <c r="O5" s="20">
-        <v>34.5505</v>
-      </c>
-      <c r="P5" s="21">
-        <v>0.217</v>
-      </c>
-      <c r="Q5" s="21">
-        <v>1.389</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="21"/>
       <c r="R5" s="21"/>
-      <c r="S5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="T5" s="12">
-        <v>1</v>
-      </c>
-      <c r="U5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="4"/>
     </row>
     <row r="6" spans="1:24" s="10" customFormat="1">
-      <c r="A6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="13">
-        <v>42440</v>
-      </c>
-      <c r="E6" s="14">
-        <f t="shared" si="0"/>
-        <v>2016</v>
-      </c>
-      <c r="F6" s="14">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="H6" s="16">
-        <v>4.6527777777777779E-2</v>
-      </c>
-      <c r="I6" s="17">
-        <v>127.23175000000001</v>
-      </c>
-      <c r="J6" s="17">
-        <v>31.747033333333334</v>
-      </c>
-      <c r="K6" s="18">
-        <v>30.423999999999999</v>
-      </c>
-      <c r="L6" s="18">
-        <v>30</v>
-      </c>
-      <c r="M6" s="18">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19">
-        <v>15.952199999999999</v>
-      </c>
-      <c r="O6" s="20">
-        <v>34.5505</v>
-      </c>
-      <c r="P6" s="21">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="Q6" s="21">
-        <v>1.29</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
       <c r="R6" s="21"/>
-      <c r="S6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="T6" s="12">
-        <v>1</v>
-      </c>
-      <c r="U6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:X1" xr:uid="{0253FD36-6E03-42A4-9659-F22DA23DE40C}"/>
